--- a/artfynd/A 56203-2021 artfynd.xlsx
+++ b/artfynd/A 56203-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56203-2021 artfynd.xlsx
+++ b/artfynd/A 56203-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114511400</v>
+        <v>114511113</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490372</v>
+        <v>490452</v>
       </c>
       <c r="R2" t="n">
-        <v>6931880</v>
+        <v>6931716</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,19 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114511211</v>
+        <v>114511192</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490395</v>
+        <v>490417</v>
       </c>
       <c r="R3" t="n">
-        <v>6931841</v>
+        <v>6931760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114511192</v>
+        <v>114511211</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490417</v>
+        <v>490395</v>
       </c>
       <c r="R4" t="n">
-        <v>6931760</v>
+        <v>6931841</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,44 +978,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114510820</v>
+        <v>114511400</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1040,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490471</v>
+        <v>490372</v>
       </c>
       <c r="R5" t="n">
-        <v>6931689</v>
+        <v>6931880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,47 +1079,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114511455</v>
+        <v>114511413</v>
       </c>
       <c r="B6" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490379</v>
+        <v>490391</v>
       </c>
       <c r="R6" t="n">
-        <v>6931965</v>
+        <v>6931908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114511071</v>
+        <v>114511255</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,31 +1191,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490471</v>
+        <v>490374</v>
       </c>
       <c r="R7" t="n">
-        <v>6931689</v>
+        <v>6931855</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,17 +1256,13 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114511488</v>
+        <v>114511288</v>
       </c>
       <c r="B8" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490342</v>
+        <v>490421</v>
       </c>
       <c r="R8" t="n">
-        <v>6931981</v>
+        <v>6931877</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,11 +1355,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114511371</v>
+        <v>114511303</v>
       </c>
       <c r="B9" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490374</v>
+        <v>490396</v>
       </c>
       <c r="R9" t="n">
-        <v>6931877</v>
+        <v>6931889</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114511113</v>
+        <v>114511329</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490452</v>
+        <v>490363</v>
       </c>
       <c r="R10" t="n">
-        <v>6931716</v>
+        <v>6931875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1651,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114511329</v>
+        <v>114511488</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,13 +1622,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490363</v>
+        <v>490342</v>
       </c>
       <c r="R11" t="n">
-        <v>6931875</v>
+        <v>6931981</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114511288</v>
+        <v>114529935</v>
       </c>
       <c r="B12" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,13 +1728,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490421</v>
+        <v>490409</v>
       </c>
       <c r="R12" t="n">
-        <v>6931877</v>
+        <v>6931696</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,12 +1758,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,15 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114511303</v>
+        <v>114511071</v>
       </c>
       <c r="B13" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,26 +1802,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1906,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490396</v>
+        <v>490471</v>
       </c>
       <c r="R13" t="n">
-        <v>6931889</v>
+        <v>6931689</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1944,13 +1872,17 @@
           <t>2024-02-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,15 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114511255</v>
+        <v>114511155</v>
       </c>
       <c r="B14" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,26 +1912,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490374</v>
+        <v>490445</v>
       </c>
       <c r="R14" t="n">
-        <v>6931855</v>
+        <v>6931732</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2056,7 +1988,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,15 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114511155</v>
+        <v>114529834</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,7 +2039,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,13 +2049,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490445</v>
+        <v>490433</v>
       </c>
       <c r="R15" t="n">
-        <v>6931732</v>
+        <v>6931659</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,12 +2079,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,15 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114511413</v>
+        <v>114529924</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,26 +2122,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2228,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490391</v>
+        <v>490512</v>
       </c>
       <c r="R16" t="n">
-        <v>6931908</v>
+        <v>6931664</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,12 +2184,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,7 +2198,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2291,47 +2216,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114529834</v>
+        <v>114511455</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490433</v>
+        <v>490379</v>
       </c>
       <c r="R17" t="n">
-        <v>6931659</v>
+        <v>6931965</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,12 +2289,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,116 +2318,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>114529924</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Övre Galvattsjön , Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>490512</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6931664</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Rätan</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56203-2021 artfynd.xlsx
+++ b/artfynd/A 56203-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511113</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511303</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511329</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511488</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114529935</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511071</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511155</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2108,6 +2178,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114529834</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114529924</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,8 +2398,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114511455</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>